--- a/Assessment Questions/CDE/Big Data Advance/KAFKA and Spark/Kafka workflow/Kafka_Workflow.xlsx
+++ b/Assessment Questions/CDE/Big Data Advance/KAFKA and Spark/Kafka workflow/Kafka_Workflow.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kafka Workflow" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C) Serialize the record</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -486,10 +486,9 @@
           <t>A producer has acks=all and min.insync.replicas=2. The topic has replication factor 3. How many replicas must acknowledge before the write is considered successful?</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2 replicas (minimum in-sync replicas)</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -509,10 +508,9 @@
           <t>What is the producer setting that controls how many replicas must acknowledge a write?</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>acks</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -539,7 +537,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B) Kafka records consumer's position</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -559,10 +557,9 @@
           <t>A consumer group loses a member. What process is triggered?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rebalance</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -582,10 +579,9 @@
           <t>What is the maximum message size default in Kafka?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1 MB</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -612,7 +608,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B) Within a partition only</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -632,10 +628,9 @@
           <t>A producer with idempotence enabled sends the same message twice due to network retry. Will duplicate messages appear?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No, idempotent producers prevent duplicates</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -655,10 +650,9 @@
           <t>What protocol does Kafka use for replication?</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ISR (In-Sync Replicas) protocol</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -685,7 +679,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B) Fetching messages</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -705,10 +699,9 @@
           <t>What is the default retention period for messages in Kafka?</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7 days</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -728,10 +721,9 @@
           <t>A topic has cleanup.policy=compact. What happens to messages with the same key?</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Only the latest message per key is retained</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -758,7 +750,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B) Manage group membership and offset commits</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -778,10 +770,9 @@
           <t>What setting controls the maximum time a consumer can be inactive before being considered dead?</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>session.timeout.ms</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -808,7 +799,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C) Either time or size threshold</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -828,10 +819,9 @@
           <t>A producer fails to send a message after max retries. What happens?</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The producer throws an exception to the application</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -851,10 +841,9 @@
           <t>What is the process of moving partition leadership from one broker to another called?</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leader election</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -881,7 +870,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>B) Determines behavior when no committed offset exists</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -901,10 +890,9 @@
           <t>What is the value of auto.offset.reset that reads from the earliest available offset?</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>earliest</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -924,10 +912,9 @@
           <t>A topic has retention.ms=86400000 and retention.bytes=1073741824. Which condition triggers deletion first?</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Whichever threshold is reached first</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
